--- a/artfynd/A 47228-2022 artfynd.xlsx
+++ b/artfynd/A 47228-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47228-2022 artfynd.xlsx
+++ b/artfynd/A 47228-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15021746</v>
+        <v>108749530</v>
       </c>
       <c r="B2" t="n">
-        <v>4852</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102358</v>
+        <v>100096</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Xyletinus ater</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Creutzer, 1796)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,24 +708,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>fallfälla</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomta SO, Vstm</t>
+          <t>Tomta, grustag SO om, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587712.0468881937</v>
+        <v>587546</v>
       </c>
       <c r="R2" t="n">
-        <v>6629166.730329555</v>
+        <v>6629165</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +756,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-07-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>OrigNr 2935Metod: fallfönsterfälla</t>
+          <t>Gjusen kretsade kring en mycket  liten damm i botten på grustaget. Jag såg den på nära håll.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,26 +778,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grustäkt</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Gunnar Sjödin</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Sjödin</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -810,12 +796,7 @@
         <v>15020875</v>
       </c>
       <c r="B3" t="n">
-        <v>27453</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>26651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -856,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587712.0468881937</v>
+        <v>587712</v>
       </c>
       <c r="R3" t="n">
-        <v>6629166.730329555</v>
+        <v>6629167</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,19 +870,9 @@
           <t>2008-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -941,6 +912,229 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>15021746</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4917</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102358</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Xyletinus ater</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Creutzer, 1796)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>fallfälla</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tomta SO, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587712</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6629167</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-07-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>OrigNr 2935Metod: fallfönsterfälla</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grustäkt</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Gunnar Sjödin</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Sjödin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134051746</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tomta gård, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587501</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6628885</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Romfartuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Felix Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Tomta gård</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47228-2022 artfynd.xlsx
+++ b/artfynd/A 47228-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108749530</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15020875</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15021746</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,8 +1155,19 @@
           <t>Tomta gård</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134051746</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>